--- a/diploma/data/ZHK_statistics.xlsx
+++ b/diploma/data/ZHK_statistics.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t xml:space="preserve">SOKOLNIKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЖК "Дзен-кварталы"</t>
   </si>
 </sst>
 </file>
@@ -217,33 +220,41 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -262,749 +273,952 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AG8"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="13.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="13.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>347</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>624</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>552</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <f aca="false">(J2+K2+L2)/B2</f>
         <v>1.71757925072046</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <f aca="false">I2-J2</f>
         <v>72</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>33004</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="1" t="n">
         <v>95.1</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="Q2" s="1" t="n">
         <v>3.1</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="T2" s="1" t="n">
+      <c r="T2" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="U2" s="0" t="n">
+      <c r="U2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="W2" s="2" t="n">
         <f aca="false">U2/V2</f>
         <v>2.5</v>
       </c>
-      <c r="X2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="0" t="n">
+      <c r="X2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="1" t="n">
         <v>55.79304</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>37.542841</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>604</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>202</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>296</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="L3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4" t="n">
+      <c r="L3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="n">
         <f aca="false">(J3+K3+L3)/B3</f>
         <v>0.327814569536424</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <f aca="false">I3-J3</f>
         <v>123</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>26780</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <v>44.5</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>2.76</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>3.06</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="T3" s="1" t="n">
+      <c r="T3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="U3" s="0" t="n">
+      <c r="U3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3" s="2" t="n">
         <f aca="false">U3/V3</f>
         <v>2.4</v>
       </c>
-      <c r="X3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="0" t="n">
+      <c r="X3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1" t="n">
         <v>55.645674</v>
       </c>
-      <c r="AG3" s="5" t="n">
+      <c r="AG3" s="6" t="n">
         <v>37.641503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>479</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>648</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>388</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="n">
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <f aca="false">(J4+K4+L4)/B4</f>
         <v>0.878914405010438</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <f aca="false">I4-J4</f>
         <v>260</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>56721</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>118.4</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>3.3</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>4.75</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="T4" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4" s="2" t="n">
         <f aca="false">U4/V4</f>
         <v>2.44444444444444</v>
       </c>
-      <c r="X4" s="0" t="n">
+      <c r="X4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="0" t="n">
+      <c r="Y4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1" t="n">
         <v>55.752009</v>
       </c>
-      <c r="AG4" s="5" t="n">
+      <c r="AG4" s="6" t="n">
         <v>37.452968</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>1331</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>852</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>805</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>517</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="n">
         <f aca="false">(J5+K5+L5)/B5</f>
         <v>0.403456048084147</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <f aca="false">I5-J5</f>
         <v>288</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>52653</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>2.62</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>2.62</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="W5" s="2" t="n">
         <f aca="false">U5/V5</f>
         <v>1</v>
       </c>
-      <c r="X5" s="0" t="n">
+      <c r="X5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="0" t="n">
+      <c r="Y5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1" t="n">
         <v>55.812115</v>
       </c>
-      <c r="AG5" s="5" t="n">
+      <c r="AG5" s="6" t="n">
         <v>37.597872</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="n">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
         <f aca="false">(J6+K6+L6)/B6</f>
         <v>0</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <f aca="false">I6-J6</f>
         <v>10</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <f aca="false">33 * 146</f>
         <v>4818</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>3.95</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6" s="2" t="n">
         <f aca="false">U6/V6</f>
         <v>3</v>
       </c>
-      <c r="X6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="0" t="n">
+      <c r="X6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>55.764016</v>
       </c>
-      <c r="AG6" s="7" t="n">
+      <c r="AG6" s="6" t="n">
         <v>37.652657</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>763</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>181</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>986</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>313</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="L7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4" t="n">
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
         <f aca="false">(J7+K7+L7)/B7</f>
         <v>0.521625163826999</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <f aca="false">I7-J7</f>
         <v>673</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>60.3</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7" s="2" t="n">
         <f aca="false">U7/V7</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="X7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Z7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="0" t="n">
+      <c r="Z7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AC7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1" t="n">
         <v>55.782995</v>
       </c>
-      <c r="AG7" s="7" t="n">
+      <c r="AG7" s="6" t="n">
         <v>37.690437</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>231</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <f aca="false">(J8+K8+L8)/B8</f>
+        <v>0.565445026178011</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <v>26326</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>68.9</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="V8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <f aca="false">U8/V8</f>
+        <v>1.625</v>
+      </c>
+      <c r="X8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="0" t="n">
+        <v>55.551201</v>
+      </c>
+      <c r="AG8" s="9" t="n">
+        <v>37.476384</v>
       </c>
     </row>
   </sheetData>
